--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -626,25 +626,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -749,7 +730,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>1</v>
       </c>
@@ -796,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R5" t="n">
         <v>20</v>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,21 @@
           <t>emergency_glide_time</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ground_move_speed</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ground_accel</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>jump_power</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -619,6 +634,21 @@
           <t>float</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -726,6 +756,21 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>emergency_glide_time</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ground_move_speed</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ground_accel</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>jump_power</t>
         </is>
       </c>
     </row>
@@ -786,6 +831,15 @@
       </c>
       <c r="T5" t="n">
         <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
         <v>100</v>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -779,10 +779,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
@@ -791,7 +791,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
         <v>14</v>
@@ -806,7 +806,7 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,11 @@
           <t>jump_power</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pose_clearance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +654,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -771,6 +781,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>jump_power</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>pose_clearance</t>
         </is>
       </c>
     </row>
@@ -840,6 +855,9 @@
       </c>
       <c r="W5" t="n">
         <v>11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -857,7 +857,7 @@
         <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,11 @@
           <t>pose_clearance</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>fall_brake</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -659,6 +664,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -786,6 +796,11 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>pose_clearance</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>fall_brake</t>
         </is>
       </c>
     </row>
@@ -858,6 +873,9 @@
       </c>
       <c r="X5" t="n">
         <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,21 @@
           <t>fall_brake</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>glide_wind_lag</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>spread_wind_lag</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>dive_wind_lag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -669,6 +684,21 @@
           <t>float</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -801,6 +831,21 @@
       <c r="Y4" t="inlineStr">
         <is>
           <t>fall_brake</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>glide_wind_lag</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>spread_wind_lag</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>dive_wind_lag</t>
         </is>
       </c>
     </row>
@@ -876,6 +921,15 @@
       </c>
       <c r="Y5" t="n">
         <v>150</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,11 @@
           <t>dive_wind_lag</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>landing_lethal_speed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -699,6 +704,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -846,6 +856,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>dive_wind_lag</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>landing_lethal_speed</t>
         </is>
       </c>
     </row>
@@ -930,6 +945,9 @@
       </c>
       <c r="AB5" t="n">
         <v>3.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#SkydiveConfig.xlsx
+++ b/table/Datas/#SkydiveConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,11 @@
           <t>landing_lethal_speed</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>restitution</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -709,6 +714,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -861,6 +871,11 @@
       <c r="AC4" t="inlineStr">
         <is>
           <t>landing_lethal_speed</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>restitution</t>
         </is>
       </c>
     </row>
@@ -948,6 +963,9 @@
       </c>
       <c r="AC5" t="n">
         <v>15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
